--- a/reports/KALM-ODO-PILOT/PRODUCT-OPTION-SCORECARD.xlsx
+++ b/reports/KALM-ODO-PILOT/PRODUCT-OPTION-SCORECARD.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="1" r:id="R46097318cbd54c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; gates" sheetId="2" r:id="R39bbfd0a8a9947b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="1" r:id="R8a0eaa2dcae64981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; gates" sheetId="2" r:id="Ra94b4fae322042c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -339,48 +339,84 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="H1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="I1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="J1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="L1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
       <x:c r="M1" s="4" t="str">
-        <x:v>KALM COLLECTIVE — ODO T-SHIRT PILOT PRODUCT OPTION SCORECARD</x:v>
+        <x:v>KALM COLLECTIVE — KALM SIGNATURE OVERSIZED TEE PRODUCT OPTION SCORECARD</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Draft-only commercial assessment. A physical sample, written stock confirmation and written embroidery capacity confirmation are still required before a selection or any external commitment.</x:v>
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>Internal commercial comparison retained for audit. Munya verbally confirmed supplier availability and production support for the approved KALM Signature Oversized Tee; the current OneDayOnly application records 100 units at a normal KALM retail price of R699.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -738,7 +774,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>Yolanda commercial input</x:v>
+        <x:v>KALM embroidery commercial input</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>2026-07-16</x:v>
@@ -747,13 +783,13 @@
         <x:v>R85 per unit including VAT supplied by Munya</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Approved input; scope/capacity pending</x:v>
+        <x:v>Munya-confirmed input</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
         <x:v>Embroidery baseline</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>Written scope, stitch dimensions, lead time and daily capacity</x:v>
+        <x:v>No additional external action required for the authorised initial application</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
